--- a/Electricty_051326_1.xlsx
+++ b/Electricty_051326_1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cwp.sharepoint.com/projects/Documents/T-22-011/Task 2. Toolkit and Training Content/Calculators to Evaluate Progress/ForGitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{92F8594E-45EF-4B2D-9430-A82905414913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC6BB20-173C-4B7B-9703-B8DB62E29E9D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{92F8594E-45EF-4B2D-9430-A82905414913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF9BABD-972E-41D9-965B-DA2A36D1F916}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15720" xr2:uid="{04E6228D-1E4E-4BDC-AF31-D38CABBEC9EB}"/>
+    <workbookView xWindow="28680" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{04E6228D-1E4E-4BDC-AF31-D38CABBEC9EB}"/>
   </bookViews>
   <sheets>
-    <sheet name="eGrid2023" sheetId="1" r:id="rId1"/>
-    <sheet name="Table_8_04" sheetId="2" r:id="rId2"/>
-    <sheet name="Table_5_06_B" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -292,29 +292,17 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -324,6 +312,18 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,72 +807,72 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>24.69</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>27.61</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>25.84</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>26.27</v>
       </c>
     </row>
@@ -892,162 +892,162 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="11"/>
+      <c r="H3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="11"/>
+      <c r="J3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>23.12</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="7">
         <v>19.690000000000001</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>17.36</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="7">
         <v>15.23</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="7">
         <v>15.9</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="7">
         <v>13.48</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="7">
         <v>13.35</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="7">
         <v>11.82</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="7">
         <v>19.64</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="7">
         <v>16.88</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>29.17</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="7">
         <v>25.76</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="7">
         <v>22.88</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="7">
         <v>20.62</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="7">
         <v>11.94</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="7">
         <v>11.22</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="7">
         <v>20.45</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="7">
         <v>14.54</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="7">
         <v>24.26</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="7">
         <v>21.45</v>
       </c>
     </row>
@@ -1066,6 +1066,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Time xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+    <Project xmlns="80727368-2d85-4693-8aca-8c33fb2339f5" xsi:nil="true"/>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SourceFile xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+    <TaxCatchAll xmlns="61ea441e-408f-4c04-8adb-e628fdc370c0" xsi:nil="true"/>
+    <Notes xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Project Document" ma:contentTypeID="0x01010084099C5946FA6344AFBC08FDA28BB5E3000F2A5536EED47B428001DEFDF00DB8CF" ma:contentTypeVersion="31" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="8f6676a41b6ceaec622f6036fe6c719c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80727368-2d85-4693-8aca-8c33fb2339f5" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns4="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xmlns:ns5="61ea441e-408f-4c04-8adb-e628fdc370c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f4c24d879343d354472f72dafe6cecf9" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="80727368-2d85-4693-8aca-8c33fb2339f5"/>
@@ -1396,39 +1421,44 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Time xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-    <Project xmlns="80727368-2d85-4693-8aca-8c33fb2339f5" xsi:nil="true"/>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SourceFile xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-    <TaxCatchAll xmlns="61ea441e-408f-4c04-8adb-e628fdc370c0" xsi:nil="true"/>
-    <Notes xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B16BCD-7748-42E1-BE84-D09317210114}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{879E6309-7A41-412E-B243-98BDA3A81392}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b031f331-093e-4af9-b9a8-5fb9941cd8bc"/>
+    <ds:schemaRef ds:uri="80727368-2d85-4693-8aca-8c33fb2339f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="61ea441e-408f-4c04-8adb-e628fdc370c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EE870C-18A9-4CD3-887B-81A7DAB593E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EE870C-18A9-4CD3-887B-81A7DAB593E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{879E6309-7A41-412E-B243-98BDA3A81392}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B16BCD-7748-42E1-BE84-D09317210114}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="80727368-2d85-4693-8aca-8c33fb2339f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="b031f331-093e-4af9-b9a8-5fb9941cd8bc"/>
+    <ds:schemaRef ds:uri="61ea441e-408f-4c04-8adb-e628fdc370c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>